--- a/upload/report/test_hiraoka4.xlsx
+++ b/upload/report/test_hiraoka4.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="130">
   <si>
     <t>Purchase order items PDF to Excel</t>
   </si>
@@ -23,7 +23,16 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02 19:27:53</t>
+    <t>2024-04-03 11:34:49</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>#Order</t>
   </si>
   <si>
     <t>Num</t>
@@ -44,7 +53,16 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Product</t>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>IMPORTACIONES HIRAOKA S.A.C.</t>
+  </si>
+  <si>
+    <t>CALLE 5, MZ. D-1, LOTE 5 - COOP., LAS VER VILLA EL SALVADOR</t>
+  </si>
+  <si>
+    <t>132675</t>
   </si>
   <si>
     <t>1</t>
@@ -62,7 +80,10 @@
     <t>3,056.8800</t>
   </si>
   <si>
-    <t xml:space="preserve"> 6,113.76REFRIGERADORA LG - GB46TGT 2</t>
+    <t>6,113.76</t>
+  </si>
+  <si>
+    <t>REFRIGERADORA LG - GB46TGT</t>
   </si>
   <si>
     <t>130136</t>
@@ -77,7 +98,7 @@
     <t>55,232.62</t>
   </si>
   <si>
-    <t>REFRIGERADORA LG - GT31WPP 8 20 10</t>
+    <t>REFRIGERADORA LG - GT31WPP</t>
   </si>
   <si>
     <t>3</t>
@@ -95,7 +116,7 @@
     <t>44,723.40</t>
   </si>
   <si>
-    <t>REFRIGERADORA LG - GT33BPP 30</t>
+    <t>REFRIGERADORA LG - GT33BPP</t>
   </si>
   <si>
     <t>4</t>
@@ -113,7 +134,7 @@
     <t>67,088.80</t>
   </si>
   <si>
-    <t>REFRIGERADORA LG - GT37SGP 40</t>
+    <t>REFRIGERADORA LG - GT37SGP</t>
   </si>
   <si>
     <t>5</t>
@@ -131,7 +152,7 @@
     <t>20,873.90</t>
   </si>
   <si>
-    <t>REFRIGERADORA LG - GT39SGP1 10</t>
+    <t>REFRIGERADORA LG - GT39SGP1</t>
   </si>
   <si>
     <t>6</t>
@@ -149,7 +170,7 @@
     <t>60,688.76</t>
   </si>
   <si>
-    <t>REFRIGERADORA LG - GT51SGD 2 3 15 2</t>
+    <t>REFRIGERADORA LG - GT51SGD</t>
   </si>
   <si>
     <t>7</t>
@@ -161,7 +182,10 @@
     <t>2,684.0000</t>
   </si>
   <si>
-    <t xml:space="preserve"> 8,052.00REFRIGERADORA LG - GT57BPSX 3</t>
+    <t>8,052.00</t>
+  </si>
+  <si>
+    <t>REFRIGERADORA LG - GT57BPSX</t>
   </si>
   <si>
     <t>8</t>
@@ -176,7 +200,7 @@
     <t>27,140.54</t>
   </si>
   <si>
-    <t>REFRIGERADORA LG - LS66SPP 1 1 4 1</t>
+    <t>REFRIGERADORA LG - LS66SPP</t>
   </si>
   <si>
     <t>9</t>
@@ -191,7 +215,7 @@
     <t>38,250.90</t>
   </si>
   <si>
-    <t>REFRIGERADORA LG - LS66SDP 9</t>
+    <t>REFRIGERADORA LG - LS66SDP</t>
   </si>
   <si>
     <t>130656</t>
@@ -203,7 +227,7 @@
     <t>22,295.16</t>
   </si>
   <si>
-    <t>LAVADORA SECADORA LG - WD15BG2S 2 7</t>
+    <t>LAVADORA SECADORA LG - WD15BG2S</t>
   </si>
   <si>
     <t>11</t>
@@ -218,7 +242,7 @@
     <t>52,173.60</t>
   </si>
   <si>
-    <t>LAVADORA LG - WT16BPB 10 10 20</t>
+    <t>LAVADORA LG - WT16BPB</t>
   </si>
   <si>
     <t>12</t>
@@ -236,7 +260,7 @@
     <t>38,251.80</t>
   </si>
   <si>
-    <t>LAVADORA LG - WT25PBVS6 5 10</t>
+    <t>LAVADORA LG - WT25PBVS6</t>
   </si>
   <si>
     <t>13</t>
@@ -251,7 +275,7 @@
     <t>15,942.92</t>
   </si>
   <si>
-    <t>COCINA A GAS LG - LRGL5847S 4</t>
+    <t>COCINA A GAS LG - LRGL5847S</t>
   </si>
   <si>
     <t>14</t>
@@ -263,7 +287,10 @@
     <t>1,423.0200</t>
   </si>
   <si>
-    <t xml:space="preserve"> 7,115.10COCINA A GAS LG - LRGZ5253S 5</t>
+    <t>7,115.10</t>
+  </si>
+  <si>
+    <t>COCINA A GAS LG - LRGZ5253S</t>
   </si>
   <si>
     <t>132166</t>
@@ -272,7 +299,10 @@
     <t>1,494.2000</t>
   </si>
   <si>
-    <t xml:space="preserve"> 7,471.00COCINA A GAS LG - LRGZ5255S 5</t>
+    <t>7,471.00</t>
+  </si>
+  <si>
+    <t>COCINA A GAS LG - LRGZ5255S</t>
   </si>
   <si>
     <t>16</t>
@@ -284,7 +314,13 @@
     <t>45</t>
   </si>
   <si>
-    <t xml:space="preserve"> 363.6800 16,365.60HORNO MICROONDA LG - MH-6536GIS 15 20 10</t>
+    <t>363.6800</t>
+  </si>
+  <si>
+    <t>16,365.60</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MH-6536GIS</t>
   </si>
   <si>
     <t>17</t>
@@ -296,7 +332,13 @@
     <t>120</t>
   </si>
   <si>
-    <t xml:space="preserve"> 349.1000 41,892.00HORNO MICROONDA LG - MH7032JAS 30 30 30 30</t>
+    <t>349.1000</t>
+  </si>
+  <si>
+    <t>41,892.00</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MH7032JAS</t>
   </si>
   <si>
     <t>18</t>
@@ -305,7 +347,13 @@
     <t>109948</t>
   </si>
   <si>
-    <t xml:space="preserve"> 509.4400 22,924.80HORNO MICROONDA LG - MH-8296DIR 15 10 10 10</t>
+    <t>509.4400</t>
+  </si>
+  <si>
+    <t>22,924.80</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MH-8296DIR</t>
   </si>
   <si>
     <t>19</t>
@@ -317,7 +365,13 @@
     <t>60</t>
   </si>
   <si>
-    <t xml:space="preserve"> 327.2400 19,634.40HORNO MICROONDA LG - MS-2536GIS 30 10 20</t>
+    <t>327.2400</t>
+  </si>
+  <si>
+    <t>19,634.40</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MS-2536GIS</t>
   </si>
   <si>
     <t>20</t>
@@ -329,7 +383,10 @@
     <t>85</t>
   </si>
   <si>
-    <t xml:space="preserve"> 349.1000 29,673.50HORNO MICROONDA LG - MS-2596DIR 30 20 15 20</t>
+    <t>29,673.50</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MS-2596DIR</t>
   </si>
   <si>
     <t>21</t>
@@ -341,7 +398,13 @@
     <t>65</t>
   </si>
   <si>
-    <t xml:space="preserve"> 436.5600 28,376.40HORNO MICROONDA LG - MS-4296DIR 20 15 15 15</t>
+    <t>436.5600</t>
+  </si>
+  <si>
+    <t>28,376.40</t>
+  </si>
+  <si>
+    <t>HORNO MICROONDA LG - MS-4296DIR</t>
   </si>
 </sst>
 </file>
@@ -681,15 +744,15 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -697,7 +760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -719,456 +782,686 @@
       <c r="G4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5"/>
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
       <c r="G5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>24</v>
+      </c>
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
         <v>28</v>
       </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="H11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" t="s">
+        <v>60</v>
+      </c>
+      <c r="J12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H13" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" t="s">
         <v>42</v>
       </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>47</v>
-      </c>
-      <c r="F11"/>
-      <c r="G11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>54</v>
-      </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G14" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
+        <v>36</v>
+      </c>
+      <c r="H15" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="G17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" t="s">
+        <v>85</v>
+      </c>
+      <c r="J17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" t="s">
+        <v>89</v>
+      </c>
+      <c r="I18" t="s">
+        <v>90</v>
+      </c>
+      <c r="J18" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F18"/>
-      <c r="G18" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>33</v>
-      </c>
       <c r="E19" t="s">
-        <v>84</v>
-      </c>
-      <c r="F19"/>
+        <v>92</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
       <c r="G19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>40</v>
+      </c>
+      <c r="H19" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" t="s">
+        <v>94</v>
+      </c>
+      <c r="J19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20"/>
-      <c r="F20"/>
+        <v>96</v>
+      </c>
+      <c r="E20" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
       <c r="G20" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+        <v>98</v>
+      </c>
+      <c r="H20" t="s">
+        <v>99</v>
+      </c>
+      <c r="I20" t="s">
+        <v>100</v>
+      </c>
+      <c r="J20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
-      </c>
-      <c r="E21"/>
-      <c r="F21"/>
+        <v>102</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
       <c r="G21" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+        <v>104</v>
+      </c>
+      <c r="H21" t="s">
+        <v>105</v>
+      </c>
+      <c r="I21" t="s">
+        <v>106</v>
+      </c>
+      <c r="J21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22"/>
-      <c r="F22"/>
+        <v>108</v>
+      </c>
+      <c r="E22" t="s">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
       <c r="G22" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
+        <v>98</v>
+      </c>
+      <c r="H22" t="s">
+        <v>110</v>
+      </c>
+      <c r="I22" t="s">
+        <v>111</v>
+      </c>
+      <c r="J22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23"/>
-      <c r="F23"/>
+        <v>113</v>
+      </c>
+      <c r="E23" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
       <c r="G23" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
+        <v>115</v>
+      </c>
+      <c r="H23" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" t="s">
+        <v>117</v>
+      </c>
+      <c r="J23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
-      </c>
-      <c r="E24"/>
-      <c r="F24"/>
+        <v>119</v>
+      </c>
+      <c r="E24" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
       <c r="G24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+        <v>121</v>
+      </c>
+      <c r="H24" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" t="s">
+        <v>122</v>
+      </c>
+      <c r="J24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25"/>
-      <c r="F25"/>
+        <v>124</v>
+      </c>
+      <c r="E25" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
       <c r="G25" t="s">
-        <v>108</v>
+        <v>126</v>
+      </c>
+      <c r="H25" t="s">
+        <v>127</v>
+      </c>
+      <c r="I25" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
